--- a/Data/Heat Storage.xlsx
+++ b/Data/Heat Storage.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Benders-Decomposition/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B03AE1C-017D-4D46-A0D0-15C66C9968AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF66A62-FC15-5F45-AF3E-28B143CC24E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
   <si>
     <t>Metrics</t>
   </si>
@@ -94,6 +94,9 @@
   </si>
   <si>
     <t>Discharging efficiency</t>
+  </si>
+  <si>
+    <t>Self discharge rate</t>
   </si>
 </sst>
 </file>
@@ -452,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5344E307-70EA-9749-BC3D-54A83804696F}">
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="31.33203125" bestFit="1" customWidth="1"/>
@@ -560,6 +563,15 @@
       </c>
       <c r="B12">
         <v>0.9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13">
+        <f>1-0.005</f>
+        <v>0.995</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Heat Storage.xlsx
+++ b/Data/Heat Storage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Benders-Decomposition/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF66A62-FC15-5F45-AF3E-28B143CC24E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393C4831-079B-6144-9526-99420BEBAFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20060" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -474,8 +474,8 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>40*1000</f>
-        <v>40000</v>
+        <f>15*1000</f>
+        <v>15000</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -501,7 +501,8 @@
         <v>10</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <f>B2*0.02</f>
+        <v>300</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>

--- a/Data/Heat Storage.xlsx
+++ b/Data/Heat Storage.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emirsener/Desktop/Benders-Decomposition/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393C4831-079B-6144-9526-99420BEBAFAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D58844F-F947-8E4A-9C86-7FAB4B8CCE29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20000" xr2:uid="{EDF38AB8-B67A-6545-84A8-C231FAB8949A}"/>
   </bookViews>
   <sheets>
     <sheet name="Initial values" sheetId="7" r:id="rId1"/>
@@ -474,8 +474,8 @@
         <v>1</v>
       </c>
       <c r="B2" s="1">
-        <f>15*1000</f>
-        <v>15000</v>
+        <f>15*10000</f>
+        <v>150000</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -502,7 +502,7 @@
       </c>
       <c r="B5">
         <f>B2*0.02</f>
-        <v>300</v>
+        <v>3000</v>
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
@@ -530,8 +530,8 @@
         <v>15</v>
       </c>
       <c r="B8">
-        <f>0.0087*1000</f>
-        <v>8.6999999999999993</v>
+        <f>0.0087*10000</f>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
@@ -547,7 +547,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>1000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
